--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,10 +505,8 @@
           <t>11/10 13:00</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>325.00</t>
-        </is>
+      <c r="F2" t="n">
+        <v>325</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -521,7 +519,7 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="3">
@@ -550,10 +548,8 @@
           <t>09/10 02:00</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F3" t="n">
+        <v>200</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -566,7 +562,7 @@
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="4">
@@ -595,10 +591,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F4" t="n">
+        <v>200</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -611,7 +605,7 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="5">
@@ -640,10 +634,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F5" t="n">
+        <v>200</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -656,7 +648,7 @@
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="6">
@@ -685,10 +677,8 @@
           <t>09/10 02:00</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F6" t="n">
+        <v>200</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -701,7 +691,7 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="7">
@@ -730,10 +720,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F7" t="n">
+        <v>175</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -746,7 +734,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="8">
@@ -775,10 +763,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F8" t="n">
+        <v>175</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -791,7 +777,7 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="9">
@@ -820,10 +806,8 @@
           <t>10/10 00:00</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F9" t="n">
+        <v>200</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -836,7 +820,7 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="10">
@@ -865,10 +849,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F10" t="n">
+        <v>175</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -881,7 +863,7 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="11">
@@ -910,10 +892,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F11" t="n">
+        <v>175</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -926,7 +906,7 @@
         </is>
       </c>
       <c r="I11" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="12">
@@ -955,10 +935,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F12" t="n">
+        <v>200</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -971,7 +949,7 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="13">
@@ -1000,10 +978,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F13" t="n">
+        <v>200</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1016,7 +992,7 @@
         </is>
       </c>
       <c r="I13" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="14">
@@ -1045,10 +1021,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F14" t="n">
+        <v>175</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1061,7 +1035,7 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="15">
@@ -1090,10 +1064,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F15" t="n">
+        <v>200</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1106,7 +1078,7 @@
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="16">
@@ -1135,10 +1107,8 @@
           <t>09/10 17:30</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F16" t="n">
+        <v>175</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1151,7 +1121,7 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="17">
@@ -1180,10 +1150,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F17" t="n">
+        <v>200</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1196,7 +1164,7 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="18">
@@ -1225,10 +1193,8 @@
           <t>10/10 16:30</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F18" t="n">
+        <v>175</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1241,7 +1207,7 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="19">
@@ -1270,10 +1236,8 @@
           <t>10/10 01:00</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F19" t="n">
+        <v>200</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1286,7 +1250,7 @@
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="20">
@@ -1315,10 +1279,8 @@
           <t>10/10 00:00</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F20" t="n">
+        <v>175</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1331,7 +1293,7 @@
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="21">
@@ -1360,10 +1322,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F21" t="n">
+        <v>150</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1376,7 +1336,7 @@
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="22">
@@ -1405,10 +1365,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F22" t="n">
+        <v>175</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1421,7 +1379,7 @@
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="23">
@@ -1450,10 +1408,8 @@
           <t>09/10 23:30</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F23" t="n">
+        <v>175</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1466,7 +1422,7 @@
         </is>
       </c>
       <c r="I23" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="24">
@@ -1495,10 +1451,8 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F24" t="n">
+        <v>175</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1511,7 +1465,7 @@
         </is>
       </c>
       <c r="I24" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="25">
@@ -1540,10 +1494,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F25" t="n">
+        <v>175</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1556,7 +1508,7 @@
         </is>
       </c>
       <c r="I25" s="2" t="n">
-        <v>45939.0686691474</v>
+        <v>45939.06866914352</v>
       </c>
     </row>
     <row r="26">
@@ -1585,23 +1537,111 @@
           <t>10/10 02:00</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" t="n">
+        <v>175</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>+120%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>45939.06866914352</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Pittsburgh</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Pittsburgh Penguins – New York IslandersNHL</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>09/10 23:00</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>+120%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>45939.0686691474</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1,27%</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>+123%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>45939.12588028408</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Fehervar A</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Fehervar AV19 – Pioneers VorarlbergAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>11/10 15:30</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>140.00</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>+119%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>45939.12588028408</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1580,10 +1580,8 @@
           <t>09/10 23:00</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F27" t="n">
+        <v>175</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1596,7 +1594,7 @@
         </is>
       </c>
       <c r="I27" s="2" t="n">
-        <v>45939.12588028408</v>
+        <v>45939.12588028935</v>
       </c>
     </row>
     <row r="28">
@@ -1625,10 +1623,8 @@
           <t>11/10 15:30</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>140.00</t>
-        </is>
+      <c r="F28" t="n">
+        <v>140</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1641,7 +1637,52 @@
         </is>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45939.12588028408</v>
+        <v>45939.12588028935</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Olimpija L</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Olimpija Ljubljana – Black Wings LinzAutriche - Autriche ICE</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>10/10 17:15</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>+125%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>45939.18455292952</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1666,10 +1666,8 @@
           <t>10/10 17:15</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F29" t="n">
+        <v>150</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1682,7 +1680,97 @@
         </is>
       </c>
       <c r="I29" s="2" t="n">
-        <v>45939.18455292952</v>
+        <v>45939.18455292824</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Lowen Fran</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Lowen Frankfurt – BerlinDEL</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>+190%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>45939.22258829397</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football | Plus que 2.51re équipe | Biélorussi</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Football</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Biélorussie – DanemarkInternational - Qualif. Europe CDM</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Plus que 2.51re équipe</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>09/10 18:45</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>+171%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>45939.22258829397</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,10 +1709,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F30" t="n">
+        <v>200</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1725,7 +1723,7 @@
         </is>
       </c>
       <c r="I30" s="2" t="n">
-        <v>45939.22258829397</v>
+        <v>45939.22258829861</v>
       </c>
     </row>
     <row r="31">
@@ -1754,10 +1752,8 @@
           <t>09/10 18:45</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F31" t="n">
+        <v>175</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1770,7 +1766,52 @@
         </is>
       </c>
       <c r="I31" s="2" t="n">
-        <v>45939.22258829397</v>
+        <v>45939.22258829861</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Presov – N</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Presov – NitraSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1,38%</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>+176%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>45939.27288466621</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1795,10 +1795,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F32" t="n">
+        <v>200</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1811,7 +1809,52 @@
         </is>
       </c>
       <c r="I32" s="2" t="n">
-        <v>45939.27288466621</v>
+        <v>45939.27288466435</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Cologne Ha</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Cologne Haie – ERC IngolstadtDEL</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>10/10 17:30</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>+113%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>45939.30594977647</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1838,10 +1838,8 @@
           <t>10/10 17:30</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F33" t="n">
+        <v>150</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1854,7 +1852,97 @@
         </is>
       </c>
       <c r="I33" s="2" t="n">
-        <v>45939.30594977647</v>
+        <v>45939.30594978009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football | Plus que 3.52e équipe | Angleterre</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Football</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Angleterre – Pays de GallesMatchs amicaux internationaux</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Plus que 3.52e équipe</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>09/10 18:45</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>+262%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>45939.35357084071</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Lausanne –</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Lausanne – EHC Biel-BienneSuisse - Suisse NLA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>+191%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>45939.35357084071</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -1881,10 +1881,8 @@
           <t>09/10 18:45</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F34" t="n">
+        <v>200</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1897,7 +1895,7 @@
         </is>
       </c>
       <c r="I34" s="2" t="n">
-        <v>45939.35357084071</v>
+        <v>45939.35357084491</v>
       </c>
     </row>
     <row r="35">
@@ -1926,10 +1924,8 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F35" t="n">
+        <v>200</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1942,7 +1938,7 @@
         </is>
       </c>
       <c r="I35" s="2" t="n">
-        <v>45939.35357084071</v>
+        <v>45939.35357084491</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1941,6 +1941,51 @@
         <v>45939.35357084491</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Poprad – Z</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Poprad – ZvolenSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>10/10 16:00</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>200.00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1,40%</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>+180%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>45939.56405263885</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -1967,10 +1967,8 @@
           <t>10/10 16:00</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>200.00</t>
-        </is>
+      <c r="F36" t="n">
+        <v>200</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1983,7 +1981,7 @@
         </is>
       </c>
       <c r="I36" s="2" t="n">
-        <v>45939.56405263885</v>
+        <v>45939.56405263889</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1984,6 +1984,51 @@
         <v>45939.56405263889</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | HC Ambri P</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HC Ambri Piotta – HC Ajoie PorrentruyNational League A</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>10/10 17:45</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+160%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45939.64705574504</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2010,23 +2010,66 @@
           <t>10/10 17:45</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" t="n">
+        <v>175</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1,48%</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>+160%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>45939.64705574074</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey | Pas de buts | Winnipeg J</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Unibet(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Winnipeg Jets – Dallas StarsNHL - YYUZJR 385076e7</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>10/10 00:00</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>+160%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>45939.64705574504</v>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45939.68656548317</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2053,23 +2053,111 @@
           <t>10/10 00:00</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" t="n">
+        <v>175</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>+142%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>45939.68656548611</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Liptovsky </t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Liptovsky Mikulas – PopradSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
         <is>
           <t>175.00</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>+142%</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>45939.68656548317</v>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>+163%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>45939.72183214796</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Zvolen – P</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Zvolen – PresovSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>12/10 16:00</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>+149%</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>45939.72183214796</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -2096,10 +2096,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F39" t="n">
+        <v>175</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2112,7 +2110,7 @@
         </is>
       </c>
       <c r="I39" s="2" t="n">
-        <v>45939.72183214796</v>
+        <v>45939.72183215278</v>
       </c>
     </row>
     <row r="40">
@@ -2141,10 +2139,8 @@
           <t>12/10 16:00</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F40" t="n">
+        <v>175</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2157,7 +2153,7 @@
         </is>
       </c>
       <c r="I40" s="2" t="n">
-        <v>45939.72183214796</v>
+        <v>45939.72183215278</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2156,6 +2156,51 @@
         <v>45939.72183215278</v>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Michalovce</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Michalovce – Slovan BratislavaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12/10 14:30</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>175.00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>+166%</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>45939.80423869388</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -2182,10 +2182,8 @@
           <t>12/10 14:30</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>175.00</t>
-        </is>
+      <c r="F41" t="n">
+        <v>175</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2198,7 +2196,7 @@
         </is>
       </c>
       <c r="I41" s="2" t="n">
-        <v>45939.80423869388</v>
+        <v>45939.80423869213</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2199,6 +2199,51 @@
         <v>45939.80423869213</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey | Pas de buts | Nitra – Ba</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Nitra – Banska BystricaSlovaquie - Slovaquie Extraliga</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>12/10 15:00</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>+128%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>45939.88830224824</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -2225,10 +2225,8 @@
           <t>12/10 15:00</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>150.00</t>
-        </is>
+      <c r="F42" t="n">
+        <v>150</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2241,7 +2239,7 @@
         </is>
       </c>
       <c r="I42" s="2" t="n">
-        <v>45939.88830224824</v>
+        <v>45939.88830224537</v>
       </c>
     </row>
   </sheetData>

--- a/data/valuebets_database_2025-10-09.xlsx
+++ b/data/valuebets_database_2025-10-09.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2242,6 +2242,51 @@
         <v>45939.88830224537</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BetClic(FR)Hockey | Pas de buts | Salzbourg </t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>BetClic(FR)Hockey</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Salzbourg – Vienne CapitalsAutriche - Autriche ICE (ADJ98280) 385076e7</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Pas de buts</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>10/10 17:15</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>150.00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1,50%</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>+125%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>45939.97151718556</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
